--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ143"/>
+  <dimension ref="A1:AZ146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6436,55 +6436,52 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>111767811</v>
+        <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93201</v>
+        <v>93426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>685155</v>
+        <v>685435</v>
       </c>
       <c r="R56" t="n">
-        <v>7315690</v>
+        <v>7315485</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6508,12 +6505,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6522,79 +6534,75 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767811</t>
+          <t>https://artportalen.se/Sighting/137153480</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>111767952</v>
+        <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93201</v>
+        <v>93426</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>685330</v>
+        <v>685331</v>
       </c>
       <c r="R57" t="n">
-        <v>7315900</v>
+        <v>7315853</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6618,12 +6626,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6632,56 +6655,55 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767952</t>
+          <t>https://artportalen.se/Sighting/137153482</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112183690</v>
+        <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93201</v>
+        <v>93426</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -6695,10 +6717,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>685031</v>
+        <v>685188</v>
       </c>
       <c r="R58" t="n">
-        <v>7315983</v>
+        <v>7316111</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6725,12 +6747,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6761,13 +6793,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112183690</t>
+          <t>https://artportalen.se/Sighting/137153486</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112649344</v>
+        <v>111767811</v>
       </c>
       <c r="B59" t="n">
         <v>93201</v>
@@ -6796,22 +6828,26 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>685025</v>
+        <v>685155</v>
       </c>
       <c r="R59" t="n">
-        <v>7315983</v>
+        <v>7315690</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6835,12 +6871,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6856,24 +6892,24 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Amanda Tas, Heike Kontermann</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649344</t>
+          <t>https://artportalen.se/Sighting/111767811</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>113888901</v>
+        <v>111767952</v>
       </c>
       <c r="B60" t="n">
         <v>93201</v>
@@ -6901,24 +6937,27 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>685201</v>
+        <v>685330</v>
       </c>
       <c r="R60" t="n">
-        <v>7315630</v>
+        <v>7315900</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6942,17 +6981,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6961,30 +6995,31 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113888901</t>
+          <t>https://artportalen.se/Sighting/111767952</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118640778</v>
+        <v>112183690</v>
       </c>
       <c r="B61" t="n">
         <v>93201</v>
@@ -7012,20 +7047,24 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>685199</v>
+        <v>685031</v>
       </c>
       <c r="R61" t="n">
-        <v>7315633</v>
+        <v>7315983</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7049,12 +7088,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7069,28 +7113,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640778</t>
+          <t>https://artportalen.se/Sighting/112183690</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118644448</v>
+        <v>112649344</v>
       </c>
       <c r="B62" t="n">
         <v>93201</v>
@@ -7119,16 +7159,19 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>685200</v>
+        <v>685025</v>
       </c>
       <c r="R62" t="n">
-        <v>7315632</v>
+        <v>7315983</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7155,12 +7198,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7169,82 +7212,76 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas, Heike Kontermann</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644448</t>
+          <t>https://artportalen.se/Sighting/112649344</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>111767965</v>
+        <v>113888901</v>
       </c>
       <c r="B63" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>685295</v>
+        <v>685201</v>
       </c>
       <c r="R63" t="n">
-        <v>7315770</v>
+        <v>7315630</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7268,12 +7305,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-09-21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7282,76 +7324,68 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767965</t>
+          <t>https://artportalen.se/Sighting/113888901</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>111767888</v>
+        <v>118640778</v>
       </c>
       <c r="B64" t="n">
-        <v>93223</v>
+        <v>93201</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5448</v>
+        <v>4365</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>685155</v>
+        <v>685199</v>
       </c>
       <c r="R64" t="n">
-        <v>7315690</v>
+        <v>7315633</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7378,12 +7412,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7392,34 +7426,37 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767888</t>
+          <t>https://artportalen.se/Sighting/118640778</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112649360</v>
+        <v>118644448</v>
       </c>
       <c r="B65" t="n">
-        <v>79327</v>
+        <v>93201</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7427,21 +7464,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7451,10 +7488,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>685303</v>
+        <v>685200</v>
       </c>
       <c r="R65" t="n">
-        <v>7316193</v>
+        <v>7315632</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7481,12 +7518,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7501,55 +7538,59 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649360</t>
+          <t>https://artportalen.se/Sighting/118644448</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>113078233</v>
+        <v>111767965</v>
       </c>
       <c r="B66" t="n">
-        <v>79327</v>
+        <v>93209</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -7560,10 +7601,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>685430</v>
+        <v>685295</v>
       </c>
       <c r="R66" t="n">
-        <v>7316135</v>
+        <v>7315770</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7590,12 +7631,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7622,54 +7663,61 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113078233</t>
+          <t>https://artportalen.se/Sighting/111767965</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118640437</v>
+        <v>111767888</v>
       </c>
       <c r="B67" t="n">
-        <v>79327</v>
+        <v>93223</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>685190</v>
+        <v>685155</v>
       </c>
       <c r="R67" t="n">
-        <v>7315965</v>
+        <v>7315690</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7693,12 +7741,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7707,34 +7755,31 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640437</t>
+          <t>https://artportalen.se/Sighting/111767888</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118644453</v>
+        <v>112649360</v>
       </c>
       <c r="B68" t="n">
         <v>79327</v>
@@ -7769,10 +7814,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>685164</v>
+        <v>685303</v>
       </c>
       <c r="R68" t="n">
-        <v>7315966</v>
+        <v>7316193</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7799,12 +7844,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7819,69 +7864,72 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644453</t>
+          <t>https://artportalen.se/Sighting/112649360</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112649347</v>
+        <v>113078233</v>
       </c>
       <c r="B69" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>685348</v>
+        <v>685430</v>
       </c>
       <c r="R69" t="n">
-        <v>7316174</v>
+        <v>7316135</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7919,71 +7967,72 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649347</t>
+          <t>https://artportalen.se/Sighting/113078233</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112649348</v>
+        <v>118640437</v>
       </c>
       <c r="B70" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>685260</v>
+        <v>685190</v>
       </c>
       <c r="R70" t="n">
-        <v>7315621</v>
+        <v>7315965</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8007,12 +8056,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8027,49 +8076,53 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Linda Hanson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649348</t>
+          <t>https://artportalen.se/Sighting/118640437</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112649349</v>
+        <v>118644453</v>
       </c>
       <c r="B71" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8079,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>685289</v>
+        <v>685164</v>
       </c>
       <c r="R71" t="n">
-        <v>7315856</v>
+        <v>7315966</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8109,12 +8162,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8129,24 +8182,28 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649349</t>
+          <t>https://artportalen.se/Sighting/118644453</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112649350</v>
+        <v>112649347</v>
       </c>
       <c r="B72" t="n">
         <v>79351</v>
@@ -8181,10 +8238,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>685398</v>
+        <v>685348</v>
       </c>
       <c r="R72" t="n">
-        <v>7316092</v>
+        <v>7316174</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8242,13 +8299,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649350</t>
+          <t>https://artportalen.se/Sighting/112649347</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112649351</v>
+        <v>112649348</v>
       </c>
       <c r="B73" t="n">
         <v>79351</v>
@@ -8283,10 +8340,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>685073</v>
+        <v>685260</v>
       </c>
       <c r="R73" t="n">
-        <v>7316026</v>
+        <v>7315621</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8344,13 +8401,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649351</t>
+          <t>https://artportalen.se/Sighting/112649348</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112649352</v>
+        <v>112649349</v>
       </c>
       <c r="B74" t="n">
         <v>79351</v>
@@ -8385,10 +8442,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>685043</v>
+        <v>685289</v>
       </c>
       <c r="R74" t="n">
-        <v>7316035</v>
+        <v>7315856</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8446,54 +8503,54 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649352</t>
+          <t>https://artportalen.se/Sighting/112649349</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118640612</v>
+        <v>112649350</v>
       </c>
       <c r="B75" t="n">
-        <v>78730</v>
+        <v>79351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>685222</v>
+        <v>685398</v>
       </c>
       <c r="R75" t="n">
-        <v>7315868</v>
+        <v>7316092</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8517,12 +8574,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8537,53 +8594,49 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640612</t>
+          <t>https://artportalen.se/Sighting/112649350</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118644458</v>
+        <v>112649351</v>
       </c>
       <c r="B76" t="n">
-        <v>78730</v>
+        <v>79351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8593,10 +8646,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>685225</v>
+        <v>685073</v>
       </c>
       <c r="R76" t="n">
-        <v>7315875</v>
+        <v>7316026</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8623,12 +8676,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8643,53 +8696,49 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644458</t>
+          <t>https://artportalen.se/Sighting/112649351</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112649319</v>
+        <v>112649352</v>
       </c>
       <c r="B77" t="n">
-        <v>83307</v>
+        <v>79351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>6434</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8699,10 +8748,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>685261</v>
+        <v>685043</v>
       </c>
       <c r="R77" t="n">
-        <v>7316227</v>
+        <v>7316035</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -8760,16 +8809,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649319</t>
+          <t>https://artportalen.se/Sighting/112649352</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118640588</v>
+        <v>118640612</v>
       </c>
       <c r="B78" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8777,21 +8826,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8801,10 +8850,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>685142</v>
+        <v>685222</v>
       </c>
       <c r="R78" t="n">
-        <v>7315652</v>
+        <v>7315868</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -8866,16 +8915,16 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640588</t>
+          <t>https://artportalen.se/Sighting/118640612</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118644440</v>
+        <v>118644458</v>
       </c>
       <c r="B79" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8883,21 +8932,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8907,10 +8956,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>685139</v>
+        <v>685225</v>
       </c>
       <c r="R79" t="n">
-        <v>7315644</v>
+        <v>7315875</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8972,16 +9021,16 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644440</t>
+          <t>https://artportalen.se/Sighting/118644458</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118640601</v>
+        <v>112649319</v>
       </c>
       <c r="B80" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8989,37 +9038,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>685239</v>
+        <v>685261</v>
       </c>
       <c r="R80" t="n">
-        <v>7315772</v>
+        <v>7316227</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9043,12 +9092,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9063,31 +9112,27 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640601</t>
+          <t>https://artportalen.se/Sighting/112649319</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118640785</v>
+        <v>118640588</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9095,37 +9140,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>685195</v>
+        <v>685142</v>
       </c>
       <c r="R81" t="n">
-        <v>7315739</v>
+        <v>7315652</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9163,19 +9208,18 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -9185,16 +9229,16 @@
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640785</t>
+          <t>https://artportalen.se/Sighting/118640588</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118644450</v>
+        <v>118644440</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9202,21 +9246,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9226,10 +9270,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>685140</v>
+        <v>685139</v>
       </c>
       <c r="R82" t="n">
-        <v>7315969</v>
+        <v>7315644</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9291,16 +9335,16 @@
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644450</t>
+          <t>https://artportalen.se/Sighting/118644440</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112649321</v>
+        <v>118640601</v>
       </c>
       <c r="B83" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9308,37 +9352,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>685073</v>
+        <v>685239</v>
       </c>
       <c r="R83" t="n">
-        <v>7316045</v>
+        <v>7315772</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9362,12 +9406,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9382,27 +9426,31 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Sofia Hamrin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649321</t>
+          <t>https://artportalen.se/Sighting/118640601</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112649322</v>
+        <v>118640785</v>
       </c>
       <c r="B84" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9410,37 +9458,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>685183</v>
+        <v>685195</v>
       </c>
       <c r="R84" t="n">
-        <v>7316184</v>
+        <v>7315739</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9464,12 +9512,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9478,33 +9526,38 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649322</t>
+          <t>https://artportalen.se/Sighting/118640785</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112649323</v>
+        <v>118644450</v>
       </c>
       <c r="B85" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9512,21 +9565,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9536,10 +9589,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>685282</v>
+        <v>685140</v>
       </c>
       <c r="R85" t="n">
-        <v>7315882</v>
+        <v>7315969</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9566,12 +9619,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9586,24 +9639,28 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649323</t>
+          <t>https://artportalen.se/Sighting/118644450</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112649324</v>
+        <v>112649321</v>
       </c>
       <c r="B86" t="n">
         <v>79946</v>
@@ -9638,10 +9695,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>685141</v>
+        <v>685073</v>
       </c>
       <c r="R86" t="n">
-        <v>7315803</v>
+        <v>7316045</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9699,13 +9756,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649324</t>
+          <t>https://artportalen.se/Sighting/112649321</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112649325</v>
+        <v>112649322</v>
       </c>
       <c r="B87" t="n">
         <v>79946</v>
@@ -9740,10 +9797,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>685165</v>
+        <v>685183</v>
       </c>
       <c r="R87" t="n">
-        <v>7315817</v>
+        <v>7316184</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9801,13 +9858,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649325</t>
+          <t>https://artportalen.se/Sighting/112649322</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112649326</v>
+        <v>112649323</v>
       </c>
       <c r="B88" t="n">
         <v>79946</v>
@@ -9842,10 +9899,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>685187</v>
+        <v>685282</v>
       </c>
       <c r="R88" t="n">
-        <v>7315808</v>
+        <v>7315882</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9903,13 +9960,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649326</t>
+          <t>https://artportalen.se/Sighting/112649323</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112649327</v>
+        <v>112649324</v>
       </c>
       <c r="B89" t="n">
         <v>79946</v>
@@ -9944,10 +10001,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>685297</v>
+        <v>685141</v>
       </c>
       <c r="R89" t="n">
-        <v>7315988</v>
+        <v>7315803</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -10005,13 +10062,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649327</t>
+          <t>https://artportalen.se/Sighting/112649324</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118640430</v>
+        <v>112649325</v>
       </c>
       <c r="B90" t="n">
         <v>79946</v>
@@ -10042,17 +10099,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Suddesjávrrie, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>685242</v>
+        <v>685165</v>
       </c>
       <c r="R90" t="n">
-        <v>7315784</v>
+        <v>7315817</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10076,12 +10133,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10096,28 +10153,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Linda Hanson</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640430</t>
+          <t>https://artportalen.se/Sighting/112649325</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>118640590</v>
+        <v>112649326</v>
       </c>
       <c r="B91" t="n">
         <v>79946</v>
@@ -10148,17 +10201,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>685237</v>
+        <v>685187</v>
       </c>
       <c r="R91" t="n">
-        <v>7315783</v>
+        <v>7315808</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10182,12 +10235,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10202,28 +10255,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640590</t>
+          <t>https://artportalen.se/Sighting/112649326</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>118640591</v>
+        <v>112649327</v>
       </c>
       <c r="B92" t="n">
         <v>79946</v>
@@ -10254,17 +10303,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>685079</v>
+        <v>685297</v>
       </c>
       <c r="R92" t="n">
-        <v>7316003</v>
+        <v>7315988</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10288,12 +10337,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10308,28 +10357,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640591</t>
+          <t>https://artportalen.se/Sighting/112649327</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118640592</v>
+        <v>118640430</v>
       </c>
       <c r="B93" t="n">
         <v>79946</v>
@@ -10360,14 +10405,14 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjávrrie, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>685017</v>
+        <v>685242</v>
       </c>
       <c r="R93" t="n">
-        <v>7316004</v>
+        <v>7315784</v>
       </c>
       <c r="S93" t="n">
         <v>1</v>
@@ -10414,12 +10459,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Linda Hanson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -10429,13 +10474,13 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640592</t>
+          <t>https://artportalen.se/Sighting/118640430</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118640773</v>
+        <v>118640590</v>
       </c>
       <c r="B94" t="n">
         <v>79946</v>
@@ -10466,17 +10511,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>685201</v>
+        <v>685237</v>
       </c>
       <c r="R94" t="n">
-        <v>7315735</v>
+        <v>7315783</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10520,12 +10565,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10535,13 +10580,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640773</t>
+          <t>https://artportalen.se/Sighting/118640590</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118640774</v>
+        <v>118640591</v>
       </c>
       <c r="B95" t="n">
         <v>79946</v>
@@ -10572,17 +10617,17 @@
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>685022</v>
+        <v>685079</v>
       </c>
       <c r="R95" t="n">
-        <v>7316004</v>
+        <v>7316003</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10626,12 +10671,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10641,13 +10686,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640774</t>
+          <t>https://artportalen.se/Sighting/118640591</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118644443</v>
+        <v>118640592</v>
       </c>
       <c r="B96" t="n">
         <v>79946</v>
@@ -10678,17 +10723,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>685022</v>
+        <v>685017</v>
       </c>
       <c r="R96" t="n">
-        <v>7316011</v>
+        <v>7316004</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10732,12 +10777,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10747,54 +10792,54 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644443</t>
+          <t>https://artportalen.se/Sighting/118640592</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>112649353</v>
+        <v>118640773</v>
       </c>
       <c r="B97" t="n">
-        <v>80460</v>
+        <v>79946</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>685266</v>
+        <v>685201</v>
       </c>
       <c r="R97" t="n">
-        <v>7315985</v>
+        <v>7315735</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10818,12 +10863,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10838,65 +10883,69 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649353</t>
+          <t>https://artportalen.se/Sighting/118640773</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>112649354</v>
+        <v>118640774</v>
       </c>
       <c r="B98" t="n">
-        <v>80460</v>
+        <v>79946</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>685211</v>
+        <v>685022</v>
       </c>
       <c r="R98" t="n">
-        <v>7316000</v>
+        <v>7316004</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10920,12 +10969,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10940,27 +10989,31 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649354</t>
+          <t>https://artportalen.se/Sighting/118640774</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>112649367</v>
+        <v>118644443</v>
       </c>
       <c r="B99" t="n">
-        <v>78334</v>
+        <v>79946</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10968,21 +11021,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10992,10 +11045,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>685183</v>
+        <v>685022</v>
       </c>
       <c r="R99" t="n">
-        <v>7316184</v>
+        <v>7316011</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11022,12 +11075,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11042,49 +11095,53 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649367</t>
+          <t>https://artportalen.se/Sighting/118644443</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>112649368</v>
+        <v>112649353</v>
       </c>
       <c r="B100" t="n">
-        <v>78334</v>
+        <v>80460</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6487</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11094,10 +11151,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>685245</v>
+        <v>685266</v>
       </c>
       <c r="R100" t="n">
-        <v>7315824</v>
+        <v>7315985</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -11155,38 +11212,38 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649368</t>
+          <t>https://artportalen.se/Sighting/112649353</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>112649369</v>
+        <v>112649354</v>
       </c>
       <c r="B101" t="n">
-        <v>78334</v>
+        <v>80460</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6487</v>
+        <v>6461</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11196,10 +11253,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>685164</v>
+        <v>685211</v>
       </c>
       <c r="R101" t="n">
-        <v>7315857</v>
+        <v>7316000</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11257,13 +11314,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649369</t>
+          <t>https://artportalen.se/Sighting/112649354</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118640610</v>
+        <v>112649367</v>
       </c>
       <c r="B102" t="n">
         <v>78334</v>
@@ -11294,17 +11351,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>685226</v>
+        <v>685183</v>
       </c>
       <c r="R102" t="n">
-        <v>7315821</v>
+        <v>7316184</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11328,12 +11385,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11348,28 +11405,24 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640610</t>
+          <t>https://artportalen.se/Sighting/112649367</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118640611</v>
+        <v>112649368</v>
       </c>
       <c r="B103" t="n">
         <v>78334</v>
@@ -11400,17 +11453,17 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>685210</v>
+        <v>685245</v>
       </c>
       <c r="R103" t="n">
-        <v>7315857</v>
+        <v>7315824</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11434,12 +11487,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11454,28 +11507,24 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640611</t>
+          <t>https://artportalen.se/Sighting/112649368</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118642384</v>
+        <v>112649369</v>
       </c>
       <c r="B104" t="n">
         <v>78334</v>
@@ -11506,17 +11555,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>685281</v>
+        <v>685164</v>
       </c>
       <c r="R104" t="n">
-        <v>7315800</v>
+        <v>7315857</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11540,12 +11589,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11560,28 +11609,24 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118642384</t>
+          <t>https://artportalen.se/Sighting/112649369</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118642386</v>
+        <v>118640610</v>
       </c>
       <c r="B105" t="n">
         <v>78334</v>
@@ -11616,13 +11661,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>685239</v>
+        <v>685226</v>
       </c>
       <c r="R105" t="n">
-        <v>7315866</v>
+        <v>7315821</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11666,12 +11711,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11681,13 +11726,13 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118642386</t>
+          <t>https://artportalen.se/Sighting/118640610</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118644457</v>
+        <v>118640611</v>
       </c>
       <c r="B106" t="n">
         <v>78334</v>
@@ -11718,17 +11763,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>685225</v>
+        <v>685210</v>
       </c>
       <c r="R106" t="n">
-        <v>7315875</v>
+        <v>7315857</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11772,12 +11817,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11787,54 +11832,54 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644457</t>
+          <t>https://artportalen.se/Sighting/118640611</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>112649341</v>
+        <v>118642384</v>
       </c>
       <c r="B107" t="n">
-        <v>57950</v>
+        <v>78334</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>685355</v>
+        <v>685281</v>
       </c>
       <c r="R107" t="n">
-        <v>7315913</v>
+        <v>7315800</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11858,12 +11903,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11878,65 +11923,69 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649341</t>
+          <t>https://artportalen.se/Sighting/118642384</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112649342</v>
+        <v>118642386</v>
       </c>
       <c r="B108" t="n">
-        <v>57950</v>
+        <v>78334</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>685337</v>
+        <v>685239</v>
       </c>
       <c r="R108" t="n">
-        <v>7315952</v>
+        <v>7315866</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11960,12 +12009,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11980,49 +12029,53 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649342</t>
+          <t>https://artportalen.se/Sighting/118642386</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112649343</v>
+        <v>118644457</v>
       </c>
       <c r="B109" t="n">
-        <v>57950</v>
+        <v>78334</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12032,10 +12085,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>685332</v>
+        <v>685225</v>
       </c>
       <c r="R109" t="n">
-        <v>7316202</v>
+        <v>7315875</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12062,17 +12115,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12087,44 +12135,48 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649343</t>
+          <t>https://artportalen.se/Sighting/118644457</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>111768033</v>
+        <v>112649341</v>
       </c>
       <c r="B110" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12133,27 +12185,19 @@
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>685359</v>
+        <v>685355</v>
       </c>
       <c r="R110" t="n">
-        <v>7315620</v>
+        <v>7315913</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12177,17 +12221,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>ringhack i gammeltall</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12202,44 +12241,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111768033</t>
+          <t>https://artportalen.se/Sighting/112649341</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>113078271</v>
+        <v>112649342</v>
       </c>
       <c r="B111" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -12248,27 +12287,19 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>684990</v>
+        <v>685337</v>
       </c>
       <c r="R111" t="n">
-        <v>7316005</v>
+        <v>7315952</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12298,11 +12329,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12317,27 +12343,27 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113078271</t>
+          <t>https://artportalen.se/Sighting/112649342</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118644445</v>
+        <v>112649343</v>
       </c>
       <c r="B112" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12345,42 +12371,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>685198</v>
+        <v>685332</v>
       </c>
       <c r="R112" t="n">
-        <v>7315723</v>
+        <v>7316202</v>
       </c>
       <c r="S112" t="n">
         <v>15</v>
@@ -12407,17 +12425,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12432,31 +12450,27 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644445</t>
+          <t>https://artportalen.se/Sighting/112649343</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>111767946</v>
+        <v>111768033</v>
       </c>
       <c r="B113" t="n">
-        <v>5495</v>
+        <v>57953</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12464,28 +12478,31 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>101410</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12493,10 +12510,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>685175</v>
+        <v>685359</v>
       </c>
       <c r="R113" t="n">
-        <v>7315755</v>
+        <v>7315620</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12533,7 +12550,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>gnaghål på tall</t>
+          <t>ringhack i gammeltall</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12542,7 +12559,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12560,33 +12576,33 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767946</t>
+          <t>https://artportalen.se/Sighting/111768033</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>117381726</v>
+        <v>113078271</v>
       </c>
       <c r="B114" t="n">
-        <v>58327</v>
+        <v>57953</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -12594,32 +12610,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>685392</v>
+        <v>684990</v>
       </c>
       <c r="R114" t="n">
-        <v>7316006</v>
+        <v>7316005</v>
       </c>
       <c r="S114" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12643,12 +12655,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12663,69 +12680,73 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117381726</t>
+          <t>https://artportalen.se/Sighting/113078271</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>111767961</v>
+        <v>118644445</v>
       </c>
       <c r="B115" t="n">
-        <v>58057</v>
+        <v>57141</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>685415</v>
+        <v>685198</v>
       </c>
       <c r="R115" t="n">
-        <v>7315870</v>
+        <v>7315723</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12749,12 +12770,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12769,27 +12795,31 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767961</t>
+          <t>https://artportalen.se/Sighting/118644445</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>112649357</v>
+        <v>111767946</v>
       </c>
       <c r="B116" t="n">
-        <v>58057</v>
+        <v>5495</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12797,37 +12827,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103031</v>
+        <v>101410</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>685292</v>
+        <v>685175</v>
       </c>
       <c r="R116" t="n">
-        <v>7315958</v>
+        <v>7315755</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12851,17 +12886,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>2 individer</t>
+          <t>gnaghål på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12870,50 +12905,51 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649357</t>
+          <t>https://artportalen.se/Sighting/111767946</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>112649358</v>
+        <v>117381726</v>
       </c>
       <c r="B117" t="n">
-        <v>58057</v>
+        <v>58327</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -12921,20 +12957,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>685278</v>
+        <v>685392</v>
       </c>
       <c r="R117" t="n">
-        <v>7315866</v>
+        <v>7316006</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12958,17 +13006,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>2 individer</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12983,65 +13026,69 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649358</t>
+          <t>https://artportalen.se/Sighting/117381726</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>112649345</v>
+        <v>111767961</v>
       </c>
       <c r="B118" t="n">
-        <v>97989</v>
+        <v>58057</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>685344</v>
+        <v>685415</v>
       </c>
       <c r="R118" t="n">
-        <v>7316186</v>
+        <v>7315870</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13065,12 +13112,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13085,49 +13132,49 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649345</t>
+          <t>https://artportalen.se/Sighting/111767961</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>112649346</v>
+        <v>112649357</v>
       </c>
       <c r="B119" t="n">
-        <v>97989</v>
+        <v>58057</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13137,10 +13184,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>685246</v>
+        <v>685292</v>
       </c>
       <c r="R119" t="n">
-        <v>7315990</v>
+        <v>7315958</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13175,6 +13222,11 @@
           <t>2023-10-10</t>
         </is>
       </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>2 individer</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13198,58 +13250,54 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649346</t>
+          <t>https://artportalen.se/Sighting/112649357</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>117381608</v>
+        <v>112649358</v>
       </c>
       <c r="B120" t="n">
-        <v>97989</v>
+        <v>58057</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>685392</v>
+        <v>685278</v>
       </c>
       <c r="R120" t="n">
-        <v>7316006</v>
+        <v>7315866</v>
       </c>
       <c r="S120" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13273,12 +13321,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>2 individer</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13287,34 +13340,33 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117381608</t>
+          <t>https://artportalen.se/Sighting/112649358</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>117381618</v>
+        <v>112649345</v>
       </c>
       <c r="B121" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13322,16 +13374,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -13340,23 +13392,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>685392</v>
+        <v>685344</v>
       </c>
       <c r="R121" t="n">
-        <v>7316006</v>
+        <v>7316186</v>
       </c>
       <c r="S121" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13380,12 +13428,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13394,72 +13442,68 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Roger Marklund</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117381618</t>
+          <t>https://artportalen.se/Sighting/112649345</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>112649356</v>
+        <v>112649346</v>
       </c>
       <c r="B122" t="n">
-        <v>79085</v>
+        <v>97989</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>685219</v>
+        <v>685246</v>
       </c>
       <c r="R122" t="n">
-        <v>7315655</v>
+        <v>7315990</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13500,7 +13544,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
@@ -13512,60 +13555,64 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Amanda Tas, Heike Kontermann, Mikael Hägg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649356</t>
+          <t>https://artportalen.se/Sighting/112649346</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118640600</v>
+        <v>117381608</v>
       </c>
       <c r="B123" t="n">
-        <v>79085</v>
+        <v>97989</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>685180</v>
+        <v>685392</v>
       </c>
       <c r="R123" t="n">
-        <v>7315662</v>
+        <v>7316006</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13589,12 +13636,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13603,78 +13650,76 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640600</t>
+          <t>https://artportalen.se/Sighting/117381608</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118640783</v>
+        <v>117381618</v>
       </c>
       <c r="B124" t="n">
-        <v>79085</v>
+        <v>97983</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>685195</v>
+        <v>685392</v>
       </c>
       <c r="R124" t="n">
-        <v>7315735</v>
+        <v>7316006</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13698,12 +13743,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13719,28 +13764,24 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Roger Marklund</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Roger Marklund</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640783</t>
+          <t>https://artportalen.se/Sighting/117381618</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118642377</v>
+        <v>112649356</v>
       </c>
       <c r="B125" t="n">
         <v>79085</v>
@@ -13769,19 +13810,22 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>685147</v>
+        <v>685219</v>
       </c>
       <c r="R125" t="n">
-        <v>7315691</v>
+        <v>7315655</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13805,12 +13849,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13819,37 +13863,34 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas, Heike Kontermann, Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118642377</t>
+          <t>https://artportalen.se/Sighting/112649356</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>112649328</v>
+        <v>118640600</v>
       </c>
       <c r="B126" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13857,37 +13898,37 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>685205</v>
+        <v>685180</v>
       </c>
       <c r="R126" t="n">
-        <v>7316168</v>
+        <v>7315662</v>
       </c>
       <c r="S126" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13911,12 +13952,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13931,27 +13972,31 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Sofia Hamrin</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649328</t>
+          <t>https://artportalen.se/Sighting/118640600</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>112649329</v>
+        <v>118640783</v>
       </c>
       <c r="B127" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13959,37 +14004,40 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>685348</v>
+        <v>685195</v>
       </c>
       <c r="R127" t="n">
-        <v>7316174</v>
+        <v>7315735</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14013,12 +14061,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14027,33 +14075,38 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649329</t>
+          <t>https://artportalen.se/Sighting/118640783</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>112649330</v>
+        <v>118642377</v>
       </c>
       <c r="B128" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14061,37 +14114,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>685279</v>
+        <v>685147</v>
       </c>
       <c r="R128" t="n">
-        <v>7315869</v>
+        <v>7315691</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14115,12 +14168,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14135,24 +14188,28 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649330</t>
+          <t>https://artportalen.se/Sighting/118642377</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>112649331</v>
+        <v>112649328</v>
       </c>
       <c r="B129" t="n">
         <v>79917</v>
@@ -14187,10 +14244,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>685260</v>
+        <v>685205</v>
       </c>
       <c r="R129" t="n">
-        <v>7315619</v>
+        <v>7316168</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14248,13 +14305,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649331</t>
+          <t>https://artportalen.se/Sighting/112649328</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>112649332</v>
+        <v>112649329</v>
       </c>
       <c r="B130" t="n">
         <v>79917</v>
@@ -14289,10 +14346,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>685299</v>
+        <v>685348</v>
       </c>
       <c r="R130" t="n">
-        <v>7315987</v>
+        <v>7316174</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14350,13 +14407,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649332</t>
+          <t>https://artportalen.se/Sighting/112649329</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>112649333</v>
+        <v>112649330</v>
       </c>
       <c r="B131" t="n">
         <v>79917</v>
@@ -14391,10 +14448,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>685040</v>
+        <v>685279</v>
       </c>
       <c r="R131" t="n">
-        <v>7316033</v>
+        <v>7315869</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14452,13 +14509,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649333</t>
+          <t>https://artportalen.se/Sighting/112649330</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>112649334</v>
+        <v>112649331</v>
       </c>
       <c r="B132" t="n">
         <v>79917</v>
@@ -14493,10 +14550,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>685294</v>
+        <v>685260</v>
       </c>
       <c r="R132" t="n">
-        <v>7315596</v>
+        <v>7315619</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14554,13 +14611,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649334</t>
+          <t>https://artportalen.se/Sighting/112649331</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118640594</v>
+        <v>112649332</v>
       </c>
       <c r="B133" t="n">
         <v>79917</v>
@@ -14591,17 +14648,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>685213</v>
+        <v>685299</v>
       </c>
       <c r="R133" t="n">
-        <v>7315728</v>
+        <v>7315987</v>
       </c>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14625,12 +14682,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14645,28 +14702,24 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640594</t>
+          <t>https://artportalen.se/Sighting/112649332</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118640595</v>
+        <v>112649333</v>
       </c>
       <c r="B134" t="n">
         <v>79917</v>
@@ -14697,17 +14750,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>685042</v>
+        <v>685040</v>
       </c>
       <c r="R134" t="n">
-        <v>7316018</v>
+        <v>7316033</v>
       </c>
       <c r="S134" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14731,12 +14784,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14751,28 +14804,24 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640595</t>
+          <t>https://artportalen.se/Sighting/112649333</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118640775</v>
+        <v>112649334</v>
       </c>
       <c r="B135" t="n">
         <v>79917</v>
@@ -14803,17 +14852,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>685170</v>
+        <v>685294</v>
       </c>
       <c r="R135" t="n">
-        <v>7315649</v>
+        <v>7315596</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14837,12 +14886,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14857,28 +14906,24 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640775</t>
+          <t>https://artportalen.se/Sighting/112649334</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118640776</v>
+        <v>118640594</v>
       </c>
       <c r="B136" t="n">
         <v>79917</v>
@@ -14909,17 +14954,17 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Suddesjsure, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>685197</v>
+        <v>685213</v>
       </c>
       <c r="R136" t="n">
-        <v>7315733</v>
+        <v>7315728</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14963,12 +15008,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Requin</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14978,13 +15023,13 @@
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118640776</t>
+          <t>https://artportalen.se/Sighting/118640594</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118642374</v>
+        <v>118640595</v>
       </c>
       <c r="B137" t="n">
         <v>79917</v>
@@ -15022,10 +15067,10 @@
         <v>685042</v>
       </c>
       <c r="R137" t="n">
-        <v>7316013</v>
+        <v>7316018</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -15069,12 +15114,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Mikael Hägg</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -15084,13 +15129,13 @@
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118642374</t>
+          <t>https://artportalen.se/Sighting/118640595</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118644444</v>
+        <v>118640775</v>
       </c>
       <c r="B138" t="n">
         <v>79917</v>
@@ -15121,17 +15166,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>685043</v>
+        <v>685170</v>
       </c>
       <c r="R138" t="n">
-        <v>7316017</v>
+        <v>7315649</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15175,12 +15220,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -15190,58 +15235,51 @@
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118644444</t>
+          <t>https://artportalen.se/Sighting/118640775</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>111767869</v>
+        <v>118640776</v>
       </c>
       <c r="B139" t="n">
-        <v>93228</v>
+        <v>79917</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjsure, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>685155</v>
+        <v>685197</v>
       </c>
       <c r="R139" t="n">
-        <v>7315690</v>
+        <v>7315733</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15268,12 +15306,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15282,34 +15320,37 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Lisa Requin</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>Lisa Requin</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767869</t>
+          <t>https://artportalen.se/Sighting/118640776</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>112649338</v>
+        <v>118642374</v>
       </c>
       <c r="B140" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15317,37 +15358,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Suddesjaur, Pi lm</t>
+          <t>Suddesjaure, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>685212</v>
+        <v>685042</v>
       </c>
       <c r="R140" t="n">
-        <v>7316204</v>
+        <v>7316013</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15371,12 +15412,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15391,27 +15432,31 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112649338</t>
+          <t>https://artportalen.se/Sighting/118642374</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>111767613</v>
+        <v>118644444</v>
       </c>
       <c r="B141" t="n">
-        <v>83173</v>
+        <v>79917</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15419,44 +15464,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1312</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>685560</v>
+        <v>685043</v>
       </c>
       <c r="R141" t="n">
-        <v>7315545</v>
+        <v>7316017</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15480,12 +15518,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15494,56 +15532,59 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY141" t="inlineStr"/>
+          <t>Bertil Svensson</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767613</t>
+          <t>https://artportalen.se/Sighting/118644444</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>111767593</v>
+        <v>111767869</v>
       </c>
       <c r="B142" t="n">
-        <v>93197</v>
+        <v>93228</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15560,10 +15601,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>685505</v>
+        <v>685155</v>
       </c>
       <c r="R142" t="n">
-        <v>7315615</v>
+        <v>7315690</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15622,16 +15663,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111767593</t>
+          <t>https://artportalen.se/Sighting/111767869</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>114799897</v>
+        <v>112649338</v>
       </c>
       <c r="B143" t="n">
-        <v>57953</v>
+        <v>79350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15639,45 +15680,37 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>260591</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Suddesjaure, Pi lm</t>
+          <t>Suddesjaur, Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>685548</v>
+        <v>685212</v>
       </c>
       <c r="R143" t="n">
-        <v>7315601</v>
+        <v>7316204</v>
       </c>
       <c r="S143" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15701,17 +15734,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>barksprätt i gran</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15726,16 +15754,351 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112649338</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>111767613</v>
+      </c>
+      <c r="B144" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Suddesjaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>685560</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7315545</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767613</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>111767593</v>
+      </c>
+      <c r="B145" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Suddesjaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>685505</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7315615</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111767593</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>114799897</v>
+      </c>
+      <c r="B146" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Suddesjaure, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>685548</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7315601</v>
+      </c>
+      <c r="S146" t="n">
+        <v>50</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>barksprätt i gran</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/114799897</t>
         </is>
@@ -15885,6 +16248,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 34531-2023 artfynd.xlsx
+++ b/artfynd/A 34531-2023 artfynd.xlsx
@@ -6439,7 +6439,7 @@
         <v>137153480</v>
       </c>
       <c r="B56" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>137153482</v>
       </c>
       <c r="B57" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>137153486</v>
       </c>
       <c r="B58" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
